--- a/resource/table/vocabulary_word_rows.xlsx
+++ b/resource/table/vocabulary_word_rows.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\work\LVPD_Studio\resource\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{587249AC-FDD8-4366-B352-E0627782C98B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4BAB5FD-30A8-44C9-B0E3-8366D24BD0B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-29310" yWindow="2100" windowWidth="27180" windowHeight="15570" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -614,7 +614,7 @@
         <v>7</v>
       </c>
       <c r="C8">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>4</v>

--- a/resource/table/vocabulary_word_rows.xlsx
+++ b/resource/table/vocabulary_word_rows.xlsx
@@ -8,24 +8,33 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\work\LVPD_Studio\resource\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4BAB5FD-30A8-44C9-B0E3-8366D24BD0B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5E46E15-9F0E-4D0D-A7C9-70633E60BBB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-29310" yWindow="2100" windowWidth="27180" windowHeight="15570" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-32955" yWindow="4950" windowWidth="27180" windowHeight="10935" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="11">
   <si>
     <t>word_id</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -42,10 +51,6 @@
     <t>desc</t>
   </si>
   <si>
-    <t>"00"</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>苹果</t>
   </si>
   <si>
@@ -57,15 +62,18 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>pronunciation_mask</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>id</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>"0"</t>
+    <t>shi</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>demonstrative</t>
+  </si>
+  <si>
+    <t>demonstrative</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -73,7 +81,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -123,12 +131,6 @@
       <family val="3"/>
       <charset val="129"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Segoe UI"/>
-      <family val="2"/>
-    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -143,27 +145,12 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="medium">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FF000000"/>
-      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -175,23 +162,23 @@
   </cellStyleXfs>
   <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="보통" xfId="1" builtinId="28"/>
@@ -473,10 +460,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:H38"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12.875" customWidth="1"/>
+    <col min="1" max="1" width="13.875" bestFit="1" customWidth="1"/>
     <col min="2" max="3" width="9.875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="19.5" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="29.625" customWidth="1"/>
@@ -485,195 +472,413 @@
     <col min="8" max="8" width="11.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="7" t="s">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="4" t="s">
-        <v>9</v>
+      <c r="B1" s="5" t="s">
+        <v>7</v>
       </c>
       <c r="C1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="E1" s="4" t="s">
+      <c r="D1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="4"/>
-      <c r="H1" s="4"/>
-    </row>
-    <row r="2" spans="1:8" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
-      <c r="C2">
+      <c r="E1" s="6"/>
+      <c r="F1" s="6"/>
+      <c r="G1" s="5"/>
+      <c r="H1" s="5"/>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1">
+        <v>1</v>
+      </c>
+      <c r="C2" s="1">
         <v>501</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="2"/>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="1">
+        <v>2</v>
+      </c>
+      <c r="C3" s="1">
+        <v>504</v>
+      </c>
+      <c r="D3" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G2" s="2"/>
-      <c r="H2" s="1"/>
-    </row>
-    <row r="3" spans="1:8" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3">
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
+      <c r="G3" s="7"/>
+      <c r="H3" s="2"/>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="1">
+        <v>3</v>
+      </c>
+      <c r="C4" s="1">
+        <v>505</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E4" s="1"/>
+      <c r="F4" s="1"/>
+      <c r="G4" s="7"/>
+      <c r="H4" s="2"/>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B5" s="1">
+        <v>4</v>
+      </c>
+      <c r="C5" s="1">
+        <v>506</v>
+      </c>
+      <c r="D5" s="2"/>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B6" s="1">
+        <v>5</v>
+      </c>
+      <c r="C6" s="1">
+        <v>507</v>
+      </c>
+      <c r="D6" s="2"/>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B7" s="1">
+        <v>6</v>
+      </c>
+      <c r="C7" s="1">
+        <v>508</v>
+      </c>
+      <c r="D7" s="2"/>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A8" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B8" s="1">
+        <v>7</v>
+      </c>
+      <c r="C8" s="1">
+        <v>510</v>
+      </c>
+      <c r="D8" s="2"/>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A9" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B9" s="1">
+        <v>8</v>
+      </c>
+      <c r="C9" s="1">
+        <v>2021</v>
+      </c>
+      <c r="D9" s="2"/>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A10" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B10" s="1">
+        <v>9</v>
+      </c>
+      <c r="C10" s="1">
+        <v>2022</v>
+      </c>
+      <c r="D10" s="2"/>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A11" s="1"/>
+      <c r="B11" s="3"/>
+      <c r="C11" s="3"/>
+      <c r="D11" s="2"/>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A12" s="1"/>
+      <c r="B12" s="4"/>
+      <c r="C12" s="3"/>
+      <c r="D12" s="2"/>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A13" s="1"/>
+      <c r="B13" s="3"/>
+      <c r="C13" s="3"/>
+      <c r="D13" s="2"/>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A14" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B14" s="4">
+        <v>1</v>
+      </c>
+      <c r="C14" s="1">
+        <v>20000</v>
+      </c>
+      <c r="D14" s="2"/>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A15" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B15" s="1">
         <v>2</v>
       </c>
-      <c r="C3">
-        <v>504</v>
-      </c>
-      <c r="D3" s="1" t="s">
+      <c r="C15" s="1">
+        <v>20002</v>
+      </c>
+      <c r="D15" s="1"/>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A16" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B16" s="1">
+        <v>3</v>
+      </c>
+      <c r="C16" s="1">
+        <v>20003</v>
+      </c>
+      <c r="D16" s="1"/>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A17" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B17" s="4">
         <v>4</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="C17" s="1">
+        <v>20004</v>
+      </c>
+      <c r="D17" s="1"/>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A18" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B18" s="4">
+        <v>5</v>
+      </c>
+      <c r="C18" s="1">
+        <v>20005</v>
+      </c>
+      <c r="D18" s="1"/>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A19" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B19" s="1">
         <v>6</v>
       </c>
-      <c r="G3" s="5"/>
-      <c r="H3" s="1"/>
-    </row>
-    <row r="4" spans="1:8" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>1</v>
-      </c>
-      <c r="B4">
+      <c r="C19" s="1">
+        <v>20006</v>
+      </c>
+      <c r="D19" s="1"/>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A20" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B20" s="4">
+        <v>7</v>
+      </c>
+      <c r="C20" s="1">
+        <v>20008</v>
+      </c>
+      <c r="D20" s="1"/>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A21" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B21" s="4">
+        <v>8</v>
+      </c>
+      <c r="C21" s="1">
+        <v>20010</v>
+      </c>
+      <c r="D21" s="1"/>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A22" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B22" s="1">
+        <v>9</v>
+      </c>
+      <c r="C22" s="1">
+        <v>10000</v>
+      </c>
+      <c r="D22" s="1"/>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A23" s="1"/>
+      <c r="B23" s="1"/>
+      <c r="C23" s="1"/>
+      <c r="D23" s="1"/>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>9</v>
+      </c>
+      <c r="B27">
+        <v>1</v>
+      </c>
+      <c r="C27">
+        <v>3100</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>9</v>
+      </c>
+      <c r="B28">
+        <v>2</v>
+      </c>
+      <c r="C28">
+        <v>3101</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>9</v>
+      </c>
+      <c r="B29">
         <v>3</v>
       </c>
-      <c r="C4">
-        <v>505</v>
-      </c>
-      <c r="D4" s="1" t="s">
+      <c r="C29">
+        <v>20103</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>9</v>
+      </c>
+      <c r="B30">
         <v>4</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="C30">
+        <v>20104</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>9</v>
+      </c>
+      <c r="B31">
+        <v>5</v>
+      </c>
+      <c r="C31">
+        <v>20105</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>10</v>
+      </c>
+      <c r="B32">
+        <v>6</v>
+      </c>
+      <c r="C32">
+        <v>20106</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>9</v>
+      </c>
+      <c r="B33">
         <v>7</v>
       </c>
-      <c r="G4" s="5"/>
-      <c r="H4" s="1"/>
-    </row>
-    <row r="5" spans="1:8" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B5">
-        <v>4</v>
-      </c>
-      <c r="C5">
-        <v>506</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E5" s="1"/>
-    </row>
-    <row r="6" spans="1:8" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>1</v>
-      </c>
-      <c r="B6">
-        <v>5</v>
-      </c>
-      <c r="C6">
-        <v>507</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E6" s="1"/>
-    </row>
-    <row r="7" spans="1:8" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
-        <v>1</v>
-      </c>
-      <c r="B7">
-        <v>6</v>
-      </c>
-      <c r="C7">
-        <v>508</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E7" s="1"/>
-    </row>
-    <row r="8" spans="1:8" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
-        <v>1</v>
-      </c>
-      <c r="B8">
-        <v>7</v>
-      </c>
-      <c r="C8">
-        <v>510</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E8" s="1"/>
-    </row>
-    <row r="9" spans="1:8" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
-        <v>1</v>
-      </c>
-      <c r="B9">
-        <v>8</v>
-      </c>
-      <c r="C9">
-        <v>2021</v>
-      </c>
-      <c r="D9" s="1" t="s">
+      <c r="C33">
+        <v>20107</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>9</v>
+      </c>
+      <c r="B34">
+        <v>8</v>
+      </c>
+      <c r="C34">
+        <v>20110</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>9</v>
+      </c>
+      <c r="B35">
+        <v>9</v>
+      </c>
+      <c r="C35">
+        <v>20111</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>9</v>
+      </c>
+      <c r="B36">
         <v>10</v>
       </c>
-      <c r="E9" s="1"/>
-    </row>
-    <row r="10" spans="1:8" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" t="s">
-        <v>1</v>
-      </c>
-      <c r="B10">
-        <v>9</v>
-      </c>
-      <c r="C10">
-        <v>2022</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E10" s="1"/>
-    </row>
-    <row r="11" spans="1:8" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B11" s="2"/>
-      <c r="C11" s="2"/>
-      <c r="D11" s="1"/>
-      <c r="E11" s="1"/>
-    </row>
-    <row r="12" spans="1:8" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="3"/>
-      <c r="C12" s="2"/>
-      <c r="D12" s="1"/>
-      <c r="E12" s="1"/>
-    </row>
-    <row r="13" spans="1:8" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B13" s="2"/>
-      <c r="C13" s="2"/>
-      <c r="D13" s="1"/>
-      <c r="E13" s="1"/>
-    </row>
-    <row r="14" spans="1:8" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B14" s="3"/>
-      <c r="C14" s="2"/>
-      <c r="D14" s="1"/>
-      <c r="E14" s="1"/>
+      <c r="C36">
+        <v>20113</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>9</v>
+      </c>
+      <c r="B37">
+        <v>11</v>
+      </c>
+      <c r="C37">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>9</v>
+      </c>
+      <c r="B38">
+        <v>12</v>
+      </c>
+      <c r="C38">
+        <v>100001</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>

--- a/resource/table/vocabulary_word_rows.xlsx
+++ b/resource/table/vocabulary_word_rows.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\work\LVPD_Studio\resource\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5E46E15-9F0E-4D0D-A7C9-70633E60BBB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD79E488-3896-4E8F-9BF7-6C32014B0977}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-32955" yWindow="4950" windowWidth="27180" windowHeight="10935" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2535" yWindow="2715" windowWidth="28440" windowHeight="15285" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="12">
   <si>
     <t>word_id</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -74,6 +74,10 @@
   </si>
   <si>
     <t>demonstrative</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>where</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -160,23 +164,22 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
   </cellXfs>
@@ -460,7 +463,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H38"/>
+  <dimension ref="A1:H47"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13.875" bestFit="1" customWidth="1"/>
@@ -473,282 +476,259 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
-      <c r="G1" s="5"/>
-      <c r="H1" s="5"/>
+      <c r="E1" s="5"/>
+      <c r="F1" s="5"/>
+      <c r="G1" s="4"/>
+      <c r="H1" s="4"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="1">
-        <v>1</v>
-      </c>
-      <c r="C2" s="1">
-        <v>501</v>
-      </c>
-      <c r="D2" s="2" t="s">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>20501</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="3"/>
-      <c r="H2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="1"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="1">
+      <c r="A3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3">
         <v>2</v>
       </c>
-      <c r="C3" s="1">
-        <v>504</v>
-      </c>
-      <c r="D3" s="3" t="s">
+      <c r="C3">
+        <v>20504</v>
+      </c>
+      <c r="D3" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="E3" s="1"/>
-      <c r="F3" s="1"/>
-      <c r="G3" s="7"/>
-      <c r="H3" s="2"/>
+      <c r="G3" s="6"/>
+      <c r="H3" s="1"/>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A4" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B4" s="1">
+      <c r="A4" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4">
         <v>3</v>
       </c>
-      <c r="C4" s="1">
-        <v>505</v>
-      </c>
-      <c r="D4" s="3" t="s">
+      <c r="C4">
+        <v>20505</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E4" s="1"/>
-      <c r="F4" s="1"/>
-      <c r="G4" s="7"/>
-      <c r="H4" s="2"/>
+      <c r="G4" s="6"/>
+      <c r="H4" s="1"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A5" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B5" s="1">
+      <c r="A5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B5">
         <v>4</v>
       </c>
-      <c r="C5" s="1">
-        <v>506</v>
-      </c>
-      <c r="D5" s="2"/>
+      <c r="C5">
+        <v>20506</v>
+      </c>
+      <c r="D5" s="1"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A6" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B6" s="1">
+      <c r="A6" t="s">
+        <v>1</v>
+      </c>
+      <c r="B6">
         <v>5</v>
       </c>
-      <c r="C6" s="1">
-        <v>507</v>
-      </c>
-      <c r="D6" s="2"/>
+      <c r="C6">
+        <v>20507</v>
+      </c>
+      <c r="D6" s="1"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A7" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B7" s="1">
+      <c r="A7" t="s">
+        <v>1</v>
+      </c>
+      <c r="B7">
         <v>6</v>
       </c>
-      <c r="C7" s="1">
-        <v>508</v>
-      </c>
-      <c r="D7" s="2"/>
+      <c r="C7">
+        <v>20508</v>
+      </c>
+      <c r="D7" s="1"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A8" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B8" s="1">
+      <c r="A8" t="s">
+        <v>1</v>
+      </c>
+      <c r="B8">
         <v>7</v>
       </c>
-      <c r="C8" s="1">
-        <v>510</v>
-      </c>
-      <c r="D8" s="2"/>
+      <c r="C8">
+        <v>20510</v>
+      </c>
+      <c r="D8" s="1"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A9" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B9" s="1">
-        <v>8</v>
-      </c>
-      <c r="C9" s="1">
+      <c r="A9" t="s">
+        <v>1</v>
+      </c>
+      <c r="B9">
+        <v>8</v>
+      </c>
+      <c r="C9">
         <v>2021</v>
       </c>
-      <c r="D9" s="2"/>
+      <c r="D9" s="1"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A10" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B10" s="1">
-        <v>9</v>
-      </c>
-      <c r="C10" s="1">
+      <c r="A10" t="s">
+        <v>1</v>
+      </c>
+      <c r="B10">
+        <v>9</v>
+      </c>
+      <c r="C10">
         <v>2022</v>
       </c>
-      <c r="D10" s="2"/>
+      <c r="D10" s="1"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A11" s="1"/>
-      <c r="B11" s="3"/>
-      <c r="C11" s="3"/>
-      <c r="D11" s="2"/>
+      <c r="B11" s="2"/>
+      <c r="C11" s="2"/>
+      <c r="D11" s="1"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A12" s="1"/>
-      <c r="B12" s="4"/>
-      <c r="C12" s="3"/>
-      <c r="D12" s="2"/>
+      <c r="B12" s="3"/>
+      <c r="C12" s="2"/>
+      <c r="D12" s="1"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A13" s="1"/>
-      <c r="B13" s="3"/>
-      <c r="C13" s="3"/>
-      <c r="D13" s="2"/>
+      <c r="B13" s="2"/>
+      <c r="C13" s="2"/>
+      <c r="D13" s="1"/>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A14" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B14" s="4">
-        <v>1</v>
-      </c>
-      <c r="C14" s="1">
+      <c r="A14" t="s">
+        <v>8</v>
+      </c>
+      <c r="B14" s="3">
+        <v>1</v>
+      </c>
+      <c r="C14">
         <v>20000</v>
       </c>
-      <c r="D14" s="2"/>
+      <c r="D14" s="1"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A15" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B15" s="1">
+      <c r="A15" t="s">
+        <v>8</v>
+      </c>
+      <c r="B15">
         <v>2</v>
       </c>
-      <c r="C15" s="1">
+      <c r="C15">
         <v>20002</v>
       </c>
-      <c r="D15" s="1"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A16" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B16" s="1">
+      <c r="A16" t="s">
+        <v>8</v>
+      </c>
+      <c r="B16">
         <v>3</v>
       </c>
-      <c r="C16" s="1">
+      <c r="C16">
         <v>20003</v>
       </c>
-      <c r="D16" s="1"/>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A17" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B17" s="4">
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>8</v>
+      </c>
+      <c r="B17" s="3">
         <v>4</v>
       </c>
-      <c r="C17" s="1">
+      <c r="C17">
         <v>20004</v>
       </c>
-      <c r="D17" s="1"/>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A18" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B18" s="4">
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>8</v>
+      </c>
+      <c r="B18" s="3">
         <v>5</v>
       </c>
-      <c r="C18" s="1">
+      <c r="C18">
         <v>20005</v>
       </c>
-      <c r="D18" s="1"/>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A19" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B19" s="1">
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>8</v>
+      </c>
+      <c r="B19">
         <v>6</v>
       </c>
-      <c r="C19" s="1">
+      <c r="C19">
         <v>20006</v>
       </c>
-      <c r="D19" s="1"/>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A20" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B20" s="4">
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>8</v>
+      </c>
+      <c r="B20" s="3">
         <v>7</v>
       </c>
-      <c r="C20" s="1">
+      <c r="C20">
         <v>20008</v>
       </c>
-      <c r="D20" s="1"/>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A21" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B21" s="4">
-        <v>8</v>
-      </c>
-      <c r="C21" s="1">
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>8</v>
+      </c>
+      <c r="B21" s="3">
+        <v>8</v>
+      </c>
+      <c r="C21">
         <v>20010</v>
       </c>
-      <c r="D21" s="1"/>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A22" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B22" s="1">
-        <v>9</v>
-      </c>
-      <c r="C22" s="1">
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>8</v>
+      </c>
+      <c r="B22">
+        <v>9</v>
+      </c>
+      <c r="C22">
         <v>10000</v>
       </c>
-      <c r="D22" s="1"/>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A23" s="1"/>
-      <c r="B23" s="1"/>
-      <c r="C23" s="1"/>
-      <c r="D23" s="1"/>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>9</v>
       </c>
@@ -756,10 +736,10 @@
         <v>1</v>
       </c>
       <c r="C27">
-        <v>3100</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+        <v>5100</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>9</v>
       </c>
@@ -767,10 +747,10 @@
         <v>2</v>
       </c>
       <c r="C28">
-        <v>3101</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+        <v>5101</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>9</v>
       </c>
@@ -781,7 +761,7 @@
         <v>20103</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>9</v>
       </c>
@@ -792,7 +772,7 @@
         <v>20104</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>9</v>
       </c>
@@ -803,7 +783,7 @@
         <v>20105</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>10</v>
       </c>
@@ -878,6 +858,72 @@
       </c>
       <c r="C38">
         <v>100001</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>11</v>
+      </c>
+      <c r="B42">
+        <v>1</v>
+      </c>
+      <c r="C42">
+        <v>20115</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
+        <v>11</v>
+      </c>
+      <c r="B43">
+        <v>2</v>
+      </c>
+      <c r="C43">
+        <v>20116</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
+        <v>11</v>
+      </c>
+      <c r="B44">
+        <v>3</v>
+      </c>
+      <c r="C44">
+        <v>20124</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
+        <v>11</v>
+      </c>
+      <c r="B45">
+        <v>4</v>
+      </c>
+      <c r="C45">
+        <v>20126</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
+        <v>11</v>
+      </c>
+      <c r="B46">
+        <v>5</v>
+      </c>
+      <c r="C46">
+        <v>20127</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
+        <v>11</v>
+      </c>
+      <c r="B47">
+        <v>6</v>
+      </c>
+      <c r="C47">
+        <v>5017</v>
       </c>
     </row>
   </sheetData>

--- a/resource/table/vocabulary_word_rows.xlsx
+++ b/resource/table/vocabulary_word_rows.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\work\LVPD_Studio\resource\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD79E488-3896-4E8F-9BF7-6C32014B0977}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BFE05B1-FE5F-4A2E-8D76-C76A5E3CCDCB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2535" yWindow="2715" windowWidth="28440" windowHeight="15285" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="13">
   <si>
     <t>word_id</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -78,6 +78,10 @@
   </si>
   <si>
     <t>where</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>test</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -463,7 +467,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H47"/>
+  <dimension ref="A1:H52"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13.875" bestFit="1" customWidth="1"/>
@@ -926,6 +930,34 @@
         <v>5017</v>
       </c>
     </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A51" t="s">
+        <v>12</v>
+      </c>
+      <c r="B51">
+        <v>1</v>
+      </c>
+      <c r="C51">
+        <v>20501</v>
+      </c>
+      <c r="D51" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A52" t="s">
+        <v>12</v>
+      </c>
+      <c r="B52">
+        <v>2</v>
+      </c>
+      <c r="C52">
+        <v>20504</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/resource/table/vocabulary_word_rows.xlsx
+++ b/resource/table/vocabulary_word_rows.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\work\LVPD_Studio\resource\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BFE05B1-FE5F-4A2E-8D76-C76A5E3CCDCB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA868DD3-CB97-42FF-898B-E6678490DC53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7485" yWindow="5460" windowWidth="32745" windowHeight="12480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="14">
   <si>
     <t>word_id</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -82,6 +82,10 @@
   </si>
   <si>
     <t>test</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>hair</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -467,7 +471,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H52"/>
+  <dimension ref="A1:H59"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13.875" bestFit="1" customWidth="1"/>
@@ -930,31 +934,108 @@
         <v>5017</v>
       </c>
     </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A49" t="s">
+        <v>13</v>
+      </c>
+      <c r="B49">
+        <v>1</v>
+      </c>
+      <c r="C49">
+        <v>20117</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
+        <v>13</v>
+      </c>
+      <c r="B50">
+        <v>2</v>
+      </c>
+      <c r="C50">
+        <v>20118</v>
+      </c>
+    </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B51">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C51">
-        <v>20501</v>
-      </c>
-      <c r="D51" s="1" t="s">
-        <v>4</v>
+        <v>20120</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
+        <v>13</v>
+      </c>
+      <c r="B52">
+        <v>4</v>
+      </c>
+      <c r="C52">
+        <v>100004</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A53" t="s">
+        <v>13</v>
+      </c>
+      <c r="B53">
+        <v>5</v>
+      </c>
+      <c r="C53">
+        <v>100006</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A54" t="s">
+        <v>13</v>
+      </c>
+      <c r="B54">
+        <v>6</v>
+      </c>
+      <c r="C54">
+        <v>20119</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A55" t="s">
+        <v>13</v>
+      </c>
+      <c r="B55">
+        <v>7</v>
+      </c>
+      <c r="C55">
+        <v>5019</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A58" t="s">
         <v>12</v>
       </c>
-      <c r="B52">
+      <c r="B58">
+        <v>1</v>
+      </c>
+      <c r="C58">
+        <v>20501</v>
+      </c>
+      <c r="D58" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A59" t="s">
+        <v>12</v>
+      </c>
+      <c r="B59">
         <v>2</v>
       </c>
-      <c r="C52">
+      <c r="C59">
         <v>20504</v>
       </c>
-      <c r="D52" s="2" t="s">
+      <c r="D59" s="2" t="s">
         <v>5</v>
       </c>
     </row>

--- a/resource/table/vocabulary_word_rows.xlsx
+++ b/resource/table/vocabulary_word_rows.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\work\LVPD_Studio\resource\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA868DD3-CB97-42FF-898B-E6678490DC53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B1807B3-AAD7-4487-8EF6-558801EEC312}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7485" yWindow="5460" windowWidth="32745" windowHeight="12480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-37230" yWindow="1170" windowWidth="32745" windowHeight="17535" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/resource/table/vocabulary_word_rows.xlsx
+++ b/resource/table/vocabulary_word_rows.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\work\LVPD_Studio\resource\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B1807B3-AAD7-4487-8EF6-558801EEC312}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C0BD6A7-D3E9-408E-9AB0-C1A9B6DDBBF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-37230" yWindow="1170" windowWidth="32745" windowHeight="17535" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="15">
   <si>
     <t>word_id</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -87,6 +87,9 @@
   <si>
     <t>hair</t>
     <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>restaurant</t>
   </si>
 </sst>
 </file>
@@ -471,7 +474,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H59"/>
+  <dimension ref="A1:H101"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13.875" bestFit="1" customWidth="1"/>
@@ -934,7 +937,7 @@
         <v>5017</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>13</v>
       </c>
@@ -945,7 +948,7 @@
         <v>20117</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>13</v>
       </c>
@@ -956,7 +959,7 @@
         <v>20118</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>13</v>
       </c>
@@ -967,7 +970,7 @@
         <v>20120</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>13</v>
       </c>
@@ -978,7 +981,7 @@
         <v>100004</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>13</v>
       </c>
@@ -989,7 +992,7 @@
         <v>100006</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>13</v>
       </c>
@@ -1000,7 +1003,7 @@
         <v>20119</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>13</v>
       </c>
@@ -1011,31 +1014,218 @@
         <v>5019</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A57" t="s">
+        <v>14</v>
+      </c>
+      <c r="B57">
+        <v>1</v>
+      </c>
+      <c r="C57">
+        <v>20128</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
+        <v>14</v>
+      </c>
+      <c r="B58">
+        <v>2</v>
+      </c>
+      <c r="C58">
+        <v>20150</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A59" t="s">
+        <v>14</v>
+      </c>
+      <c r="B59">
+        <v>3</v>
+      </c>
+      <c r="C59">
+        <v>20151</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A60" t="s">
+        <v>14</v>
+      </c>
+      <c r="B60">
+        <v>4</v>
+      </c>
+      <c r="C60">
+        <v>20152</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A61" t="s">
+        <v>14</v>
+      </c>
+      <c r="B61">
+        <v>5</v>
+      </c>
+      <c r="C61">
+        <v>20135</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A62" t="s">
+        <v>14</v>
+      </c>
+      <c r="B62">
+        <v>6</v>
+      </c>
+      <c r="C62">
+        <v>20145</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A63" t="s">
+        <v>14</v>
+      </c>
+      <c r="B63">
+        <v>7</v>
+      </c>
+      <c r="C63">
+        <v>20146</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A64" t="s">
+        <v>14</v>
+      </c>
+      <c r="B64">
+        <v>8</v>
+      </c>
+      <c r="C64">
+        <v>20018</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A65" t="s">
+        <v>14</v>
+      </c>
+      <c r="B65">
+        <v>9</v>
+      </c>
+      <c r="C65">
+        <v>20017</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A66" t="s">
+        <v>14</v>
+      </c>
+      <c r="B66">
+        <v>10</v>
+      </c>
+      <c r="C66">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A67" t="s">
+        <v>14</v>
+      </c>
+      <c r="B67">
+        <v>11</v>
+      </c>
+      <c r="C67">
+        <v>2027</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A68" t="s">
+        <v>14</v>
+      </c>
+      <c r="B68">
         <v>12</v>
       </c>
-      <c r="B58">
-        <v>1</v>
-      </c>
-      <c r="C58">
+      <c r="C68">
+        <v>2028</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A69" t="s">
+        <v>14</v>
+      </c>
+      <c r="B69">
+        <v>13</v>
+      </c>
+      <c r="C69">
+        <v>10011</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A70" t="s">
+        <v>14</v>
+      </c>
+      <c r="B70">
+        <v>14</v>
+      </c>
+      <c r="C70">
+        <v>10012</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A71" t="s">
+        <v>14</v>
+      </c>
+      <c r="B71">
+        <v>15</v>
+      </c>
+      <c r="C71">
+        <v>10013</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A72" t="s">
+        <v>14</v>
+      </c>
+      <c r="B72">
+        <v>16</v>
+      </c>
+      <c r="C72">
+        <v>10014</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A73" t="s">
+        <v>14</v>
+      </c>
+      <c r="B73">
+        <v>17</v>
+      </c>
+      <c r="C73">
+        <v>10015</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A100" t="s">
+        <v>12</v>
+      </c>
+      <c r="B100">
+        <v>1</v>
+      </c>
+      <c r="C100">
         <v>20501</v>
       </c>
-      <c r="D58" s="1" t="s">
+      <c r="D100" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A59" t="s">
+    <row r="101" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A101" t="s">
         <v>12</v>
       </c>
-      <c r="B59">
+      <c r="B101">
         <v>2</v>
       </c>
-      <c r="C59">
+      <c r="C101">
         <v>20504</v>
       </c>
-      <c r="D59" s="2" t="s">
+      <c r="D101" s="2" t="s">
         <v>5</v>
       </c>
     </row>

--- a/resource/table/vocabulary_word_rows.xlsx
+++ b/resource/table/vocabulary_word_rows.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\work\LVPD_Studio\resource\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C0BD6A7-D3E9-408E-9AB0-C1A9B6DDBBF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{930DC759-04E7-40E2-9B25-37A7094F191B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="15">
   <si>
     <t>word_id</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -1132,7 +1132,7 @@
         <v>11</v>
       </c>
       <c r="C67">
-        <v>2027</v>
+        <v>2026</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.3">
@@ -1143,7 +1143,7 @@
         <v>12</v>
       </c>
       <c r="C68">
-        <v>2028</v>
+        <v>2027</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.3">
@@ -1154,7 +1154,7 @@
         <v>13</v>
       </c>
       <c r="C69">
-        <v>10011</v>
+        <v>2028</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.3">
@@ -1165,7 +1165,7 @@
         <v>14</v>
       </c>
       <c r="C70">
-        <v>10012</v>
+        <v>10011</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.3">
@@ -1176,7 +1176,7 @@
         <v>15</v>
       </c>
       <c r="C71">
-        <v>10013</v>
+        <v>10012</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.3">
@@ -1187,7 +1187,7 @@
         <v>16</v>
       </c>
       <c r="C72">
-        <v>10014</v>
+        <v>10013</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.3">
@@ -1198,6 +1198,17 @@
         <v>17</v>
       </c>
       <c r="C73">
+        <v>10014</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A74" t="s">
+        <v>14</v>
+      </c>
+      <c r="B74">
+        <v>18</v>
+      </c>
+      <c r="C74">
         <v>10015</v>
       </c>
     </row>
